--- a/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0002T0006Z000C1N10_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0002T0006Z000C1N10_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>8.556453127292817</v>
+        <v>1.390423633185083</v>
       </c>
       <c r="D2" t="n">
-        <v>7.188808160746285</v>
+        <v>1.168181326121271</v>
       </c>
       <c r="E2" t="n">
-        <v>15.3200478714147</v>
+        <v>2.48950777910489</v>
       </c>
       <c r="F2" t="n">
-        <v>12.58577149580448</v>
+        <v>2.045187868068229</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>21.28492275670978</v>
+        <v>3.45879994796534</v>
       </c>
       <c r="D3" t="n">
-        <v>24.86227089381159</v>
+        <v>4.040119020244383</v>
       </c>
       <c r="E3" t="n">
-        <v>15.3200478714147</v>
+        <v>2.48950777910489</v>
       </c>
       <c r="F3" t="n">
-        <v>12.58577149580448</v>
+        <v>2.045187868068229</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>38.32415019761361</v>
+        <v>6.227674407112212</v>
       </c>
       <c r="D4" t="n">
-        <v>27.65400815483956</v>
+        <v>4.493776325161428</v>
       </c>
       <c r="E4" t="n">
-        <v>15.3200478714147</v>
+        <v>2.48950777910489</v>
       </c>
       <c r="F4" t="n">
-        <v>12.58577149580448</v>
+        <v>2.045187868068229</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>43.8138376185413</v>
+        <v>7.119748613012962</v>
       </c>
       <c r="D5" t="n">
-        <v>39.76855570657441</v>
+        <v>6.462390302318342</v>
       </c>
       <c r="E5" t="n">
-        <v>15.3200478714147</v>
+        <v>2.48950777910489</v>
       </c>
       <c r="F5" t="n">
-        <v>12.58577149580448</v>
+        <v>2.045187868068229</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>50.1790167456952</v>
+        <v>8.154090221175471</v>
       </c>
       <c r="D6" t="n">
-        <v>42.53426630841735</v>
+        <v>6.911818275117819</v>
       </c>
       <c r="E6" t="n">
-        <v>15.3200478714147</v>
+        <v>2.48950777910489</v>
       </c>
       <c r="F6" t="n">
-        <v>12.58577149580448</v>
+        <v>2.045187868068229</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
